--- a/details.xlsx
+++ b/details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Project-Mini-Banking-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4890912-9995-4353-AF15-B455672F68A8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB912E12-0C86-4356-9D3B-A3480C7C7497}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t>account_number</t>
   </si>
@@ -43,13 +43,19 @@
     <t>balance</t>
   </si>
   <si>
-    <t>3827965705</t>
-  </si>
-  <si>
     <t>a</t>
   </si>
   <si>
-    <t>1</t>
+    <t>4666846608</t>
+  </si>
+  <si>
+    <t>2026-01-01</t>
+  </si>
+  <si>
+    <t>name@gamil.com</t>
+  </si>
+  <si>
+    <t>1122334455</t>
   </si>
 </sst>
 </file>
@@ -389,10 +395,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.1796875" customWidth="1"/>
+    <col min="1" max="1" width="17.90625" customWidth="1"/>
+    <col min="4" max="4" width="17.81640625" customWidth="1"/>
+    <col min="5" max="5" width="26.36328125" customWidth="1"/>
+    <col min="6" max="6" width="17.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -419,26 +428,49 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2">
+        <v>3827965705</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2">
         <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>500000</v>
       </c>
     </row>
   </sheetData>

--- a/details.xlsx
+++ b/details.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Project-Mini-Banking-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8007D392-9660-4050-8612-FA337A63102F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45E66C1-182B-4C94-B6C3-E5CF0AA90DCF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="3990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>account_number</t>
   </si>
@@ -46,16 +46,13 @@
     <t>2832693554</t>
   </si>
   <si>
-    <t>Vinayak</t>
+    <t>Vinayak Mishra</t>
   </si>
   <si>
     <t>2001-08-24</t>
   </si>
   <si>
     <t>abc,xyz</t>
-  </si>
-  <si>
-    <t>1122334455</t>
   </si>
   <si>
     <t>abc@gmail.com</t>
@@ -94,8 +91,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,11 +399,7 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.6328125" customWidth="1"/>
-    <col min="2" max="2" width="17.81640625" customWidth="1"/>
-    <col min="3" max="3" width="17.453125" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="17.36328125" customWidth="1"/>
+    <col min="5" max="5" width="18.08984375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -421,7 +415,7 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -444,11 +438,11 @@
       <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1">
+        <v>1122334455</v>
+      </c>
+      <c r="F2" t="s">
         <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
       </c>
       <c r="G2">
         <v>10000</v>

--- a/details.xlsx
+++ b/details.xlsx
@@ -1,79 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Project-Mini-Banking-System\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45E66C1-182B-4C94-B6C3-E5CF0AA90DCF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="3990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>account_number</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>dob</t>
-  </si>
-  <si>
-    <t>address</t>
-  </si>
-  <si>
-    <t>phone</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>balance</t>
-  </si>
-  <si>
-    <t>2832693554</t>
-  </si>
-  <si>
-    <t>Vinayak Mishra</t>
-  </si>
-  <si>
-    <t>2001-08-24</t>
-  </si>
-  <si>
-    <t>abc,xyz</t>
-  </si>
-  <si>
-    <t>abc@gmail.com</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -91,23 +46,81 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -395,56 +408,83 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="5" max="5" width="18.08984375" style="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>account_number</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>dob</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1">
-        <v>1122334455</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2832693554</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Vinayak Mishra</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2001-08-24</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>abc,xyz</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>9310413639</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>abc@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>10000</v>
       </c>
     </row>

--- a/details.xlsx
+++ b/details.xlsx
@@ -1,34 +1,82 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Project-Mini-Banking-System\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B29D28-5E16-414F-B9A2-7994648EB430}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>account_number</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>dob</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>balance</t>
+  </si>
+  <si>
+    <t>2832693554</t>
+  </si>
+  <si>
+    <t>Vinayak Mishra</t>
+  </si>
+  <si>
+    <t>2001-08-24</t>
+  </si>
+  <si>
+    <t>abc,xyz</t>
+  </si>
+  <si>
+    <t>9310413639</t>
+  </si>
+  <si>
+    <t>abc@gmail.com</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +95,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,83 +397,53 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>account_number</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>dob</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>balance</t>
-        </is>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2832693554</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Vinayak Mishra</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2001-08-24</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>abc,xyz</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>9310413639</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>abc@gmail.com</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2">
         <v>10000</v>
       </c>
     </row>

--- a/details.xlsx
+++ b/details.xlsx
@@ -1,82 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Project-Mini-Banking-System\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B29D28-5E16-414F-B9A2-7994648EB430}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>account_number</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>dob</t>
-  </si>
-  <si>
-    <t>address</t>
-  </si>
-  <si>
-    <t>phone</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>balance</t>
-  </si>
-  <si>
-    <t>2832693554</t>
-  </si>
-  <si>
-    <t>Vinayak Mishra</t>
-  </si>
-  <si>
-    <t>2001-08-24</t>
-  </si>
-  <si>
-    <t>abc,xyz</t>
-  </si>
-  <si>
-    <t>9310413639</t>
-  </si>
-  <si>
-    <t>abc@gmail.com</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -95,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -397,54 +408,115 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>account_number</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>dob</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2832693554</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Vinayak Kumar Mishra</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2000-08-24</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ghaziabad,up</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1122334455</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>up@gmail.com</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>10000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>7983161650</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Izaan alam</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>01-01-1990</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>welecome,up</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>6677889910</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>up@gmail.com</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>5000</v>
       </c>
     </row>
   </sheetData>

--- a/details.xlsx
+++ b/details.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TransactionHistory" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -516,7 +517,63 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5000</v>
+        <v>15000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Account Number</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Transaction Type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Date &amp; Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>7983161650</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-06-19 06:57:02</t>
+        </is>
       </c>
     </row>
   </sheetData>
